--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.96873635976514</v>
+        <v>9.094919658461835</v>
       </c>
       <c r="D2" t="n">
-        <v>55.94372256014512</v>
+        <v>9.090854916023583</v>
       </c>
       <c r="E2" t="n">
-        <v>16.56035485997295</v>
+        <v>2.691057664745605</v>
       </c>
       <c r="F2" t="n">
-        <v>16.73042533142063</v>
+        <v>2.718694116355852</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.50845359497602</v>
+        <v>9.020123709183602</v>
       </c>
       <c r="D3" t="n">
-        <v>55.44397540716271</v>
+        <v>9.00964600366394</v>
       </c>
       <c r="E3" t="n">
-        <v>16.56035485997295</v>
+        <v>2.691057664745605</v>
       </c>
       <c r="F3" t="n">
-        <v>16.73042533142063</v>
+        <v>2.718694116355852</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.19574591335009</v>
+        <v>7.83180871091939</v>
       </c>
       <c r="D4" t="n">
-        <v>48.14298005451673</v>
+        <v>7.823234258858968</v>
       </c>
       <c r="E4" t="n">
-        <v>16.56035485997295</v>
+        <v>2.691057664745605</v>
       </c>
       <c r="F4" t="n">
-        <v>16.73042533142063</v>
+        <v>2.718694116355852</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.34163712642013</v>
+        <v>8.830516033043272</v>
       </c>
       <c r="D5" t="n">
-        <v>54.30627502340464</v>
+        <v>8.824769691303255</v>
       </c>
       <c r="E5" t="n">
-        <v>16.56035485997295</v>
+        <v>2.691057664745605</v>
       </c>
       <c r="F5" t="n">
-        <v>16.73042533142063</v>
+        <v>2.718694116355852</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.539422332705918</v>
+        <v>1.550156129064712</v>
       </c>
       <c r="D6" t="n">
-        <v>9.013878188659973</v>
+        <v>1.464755205657246</v>
       </c>
       <c r="E6" t="n">
-        <v>16.56035485997295</v>
+        <v>2.691057664745605</v>
       </c>
       <c r="F6" t="n">
-        <v>16.73042533142063</v>
+        <v>2.718694116355852</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.21011776321441</v>
+        <v>5.884144136522341</v>
       </c>
       <c r="D7" t="n">
-        <v>36.0821383016279</v>
+        <v>5.863347474014534</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56035485997295</v>
+        <v>2.691057664745605</v>
       </c>
       <c r="F7" t="n">
-        <v>16.73042533142063</v>
+        <v>2.718694116355852</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
